--- a/artfynd/A 49634-2025 artfynd.xlsx
+++ b/artfynd/A 49634-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981503</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74769493</v>
       </c>
       <c r="B3" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74766299</v>
       </c>
       <c r="B4" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74969943</v>
       </c>
       <c r="B5" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49634-2025 artfynd.xlsx
+++ b/artfynd/A 49634-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981503</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74769493</v>
       </c>
       <c r="B3" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74766299</v>
       </c>
       <c r="B4" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74969943</v>
       </c>
       <c r="B5" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49634-2025 artfynd.xlsx
+++ b/artfynd/A 49634-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981503</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74769493</v>
       </c>
       <c r="B3" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74766299</v>
       </c>
       <c r="B4" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74969943</v>
       </c>
       <c r="B5" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49634-2025 artfynd.xlsx
+++ b/artfynd/A 49634-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981503</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74769493</v>
       </c>
       <c r="B3" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74766299</v>
       </c>
       <c r="B4" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74969943</v>
       </c>
       <c r="B5" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
